--- a/data/budget/budget.xlsx
+++ b/data/budget/budget.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\skynet\kpi_dash\data\budget\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E0A7144-80BE-4E45-A163-6217F2704893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84689FD-8E55-4FE7-8915-1B57D4B726D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED12F3B-E9C0-4CC9-BE1F-B275112E9E1C}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{DED12F3B-E9C0-4CC9-BE1F-B275112E9E1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="44">
   <si>
     <t>month</t>
   </si>
@@ -139,6 +139,39 @@
   <si>
     <t>Hugo Boss PE</t>
   </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-12</t>
+  </si>
+  <si>
+    <t>2026-11</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
 </sst>
 </file>
 
@@ -173,8 +206,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5851A3DA-8388-4BFF-8FBA-390951F75AA3}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J229"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
@@ -1156,7 +1190,6696 @@
         <v>366</v>
       </c>
     </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="1">
+        <v>22935</v>
+      </c>
+      <c r="E21">
+        <v>98883527</v>
+      </c>
+      <c r="F21">
+        <v>105569</v>
+      </c>
+      <c r="G21">
+        <v>9287145</v>
+      </c>
+      <c r="H21">
+        <v>9915</v>
+      </c>
+      <c r="I21">
+        <v>108170672</v>
+      </c>
+      <c r="J21">
+        <v>115484</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="1">
+        <v>17000</v>
+      </c>
+      <c r="E22">
+        <v>66464220</v>
+      </c>
+      <c r="F22">
+        <v>70958</v>
+      </c>
+      <c r="G22">
+        <v>11357700</v>
+      </c>
+      <c r="H22">
+        <v>12126</v>
+      </c>
+      <c r="I22">
+        <v>77821920</v>
+      </c>
+      <c r="J22">
+        <v>83084</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="1">
+        <v>4492</v>
+      </c>
+      <c r="E23">
+        <v>14400723</v>
+      </c>
+      <c r="F23">
+        <v>15375</v>
+      </c>
+      <c r="G23">
+        <v>3069833</v>
+      </c>
+      <c r="H23">
+        <v>3277</v>
+      </c>
+      <c r="I23">
+        <v>17470556</v>
+      </c>
+      <c r="J23">
+        <v>18652</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="1">
+        <v>3870</v>
+      </c>
+      <c r="E24">
+        <v>11636936</v>
+      </c>
+      <c r="F24">
+        <v>12424</v>
+      </c>
+      <c r="G24">
+        <v>1109219</v>
+      </c>
+      <c r="H24">
+        <v>1184</v>
+      </c>
+      <c r="I24">
+        <v>12746155</v>
+      </c>
+      <c r="J24">
+        <v>13608</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1548</v>
+      </c>
+      <c r="E25">
+        <v>3936347</v>
+      </c>
+      <c r="F25">
+        <v>4202</v>
+      </c>
+      <c r="G25">
+        <v>287371</v>
+      </c>
+      <c r="H25">
+        <v>307</v>
+      </c>
+      <c r="I25">
+        <v>4223718</v>
+      </c>
+      <c r="J25">
+        <v>4509</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26">
+        <v>868</v>
+      </c>
+      <c r="E26">
+        <v>2193922</v>
+      </c>
+      <c r="F26">
+        <v>2342</v>
+      </c>
+      <c r="G26">
+        <v>280659</v>
+      </c>
+      <c r="H26">
+        <v>300</v>
+      </c>
+      <c r="I26">
+        <v>2474581</v>
+      </c>
+      <c r="J26">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27">
+        <v>704</v>
+      </c>
+      <c r="E27">
+        <v>2689236</v>
+      </c>
+      <c r="F27">
+        <v>2871</v>
+      </c>
+      <c r="G27">
+        <v>470473</v>
+      </c>
+      <c r="H27">
+        <v>502</v>
+      </c>
+      <c r="I27">
+        <v>3159709</v>
+      </c>
+      <c r="J27">
+        <v>3373</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28">
+        <v>439</v>
+      </c>
+      <c r="E28">
+        <v>1422598</v>
+      </c>
+      <c r="F28">
+        <v>1518</v>
+      </c>
+      <c r="G28">
+        <v>216725</v>
+      </c>
+      <c r="H28">
+        <v>232</v>
+      </c>
+      <c r="I28">
+        <v>1639323</v>
+      </c>
+      <c r="J28">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30">
+        <v>314</v>
+      </c>
+      <c r="E30">
+        <v>992548</v>
+      </c>
+      <c r="F30">
+        <v>1059</v>
+      </c>
+      <c r="G30">
+        <v>164624</v>
+      </c>
+      <c r="H30">
+        <v>176</v>
+      </c>
+      <c r="I30">
+        <v>1157172</v>
+      </c>
+      <c r="J30">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31">
+        <v>283</v>
+      </c>
+      <c r="E31">
+        <v>1262598</v>
+      </c>
+      <c r="F31">
+        <v>1348</v>
+      </c>
+      <c r="G31">
+        <v>180413</v>
+      </c>
+      <c r="H31">
+        <v>193</v>
+      </c>
+      <c r="I31">
+        <v>1443011</v>
+      </c>
+      <c r="J31">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33">
+        <v>191</v>
+      </c>
+      <c r="E33">
+        <v>842791</v>
+      </c>
+      <c r="F33">
+        <v>900</v>
+      </c>
+      <c r="G33">
+        <v>127607</v>
+      </c>
+      <c r="H33">
+        <v>136</v>
+      </c>
+      <c r="I33">
+        <v>970398</v>
+      </c>
+      <c r="J33">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34">
+        <v>159</v>
+      </c>
+      <c r="E34">
+        <v>629096</v>
+      </c>
+      <c r="F34">
+        <v>671</v>
+      </c>
+      <c r="G34">
+        <v>83036</v>
+      </c>
+      <c r="H34">
+        <v>89</v>
+      </c>
+      <c r="I34">
+        <v>712132</v>
+      </c>
+      <c r="J34">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="1">
+        <v>8858</v>
+      </c>
+      <c r="E36">
+        <v>86471</v>
+      </c>
+      <c r="F36">
+        <v>23887</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>86471</v>
+      </c>
+      <c r="J36">
+        <v>23887</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="1">
+        <v>5442</v>
+      </c>
+      <c r="E37">
+        <v>19040</v>
+      </c>
+      <c r="F37">
+        <v>19040</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>19040</v>
+      </c>
+      <c r="J37">
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1577</v>
+      </c>
+      <c r="E38">
+        <v>20997</v>
+      </c>
+      <c r="F38">
+        <v>5800</v>
+      </c>
+      <c r="G38">
+        <v>4199</v>
+      </c>
+      <c r="H38">
+        <v>1160</v>
+      </c>
+      <c r="I38">
+        <v>25196</v>
+      </c>
+      <c r="J38">
+        <v>6960</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39">
+        <v>270</v>
+      </c>
+      <c r="E39">
+        <v>2630</v>
+      </c>
+      <c r="F39">
+        <v>726</v>
+      </c>
+      <c r="G39">
+        <v>419</v>
+      </c>
+      <c r="H39">
+        <v>116</v>
+      </c>
+      <c r="I39">
+        <v>3049</v>
+      </c>
+      <c r="J39">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="1">
+        <v>28223</v>
+      </c>
+      <c r="E40">
+        <v>121684700</v>
+      </c>
+      <c r="F40">
+        <v>130377</v>
+      </c>
+      <c r="G40">
+        <v>11428632</v>
+      </c>
+      <c r="H40">
+        <v>12245</v>
+      </c>
+      <c r="I40">
+        <v>133113332</v>
+      </c>
+      <c r="J40">
+        <v>142622</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="1">
+        <v>13415</v>
+      </c>
+      <c r="E41">
+        <v>52448871</v>
+      </c>
+      <c r="F41">
+        <v>56195</v>
+      </c>
+      <c r="G41">
+        <v>8962695</v>
+      </c>
+      <c r="H41">
+        <v>9603</v>
+      </c>
+      <c r="I41">
+        <v>61411566</v>
+      </c>
+      <c r="J41">
+        <v>65798</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>34</v>
+      </c>
+      <c r="B42" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="1">
+        <v>2624</v>
+      </c>
+      <c r="E42">
+        <v>8412176</v>
+      </c>
+      <c r="F42">
+        <v>9012</v>
+      </c>
+      <c r="G42">
+        <v>1793242</v>
+      </c>
+      <c r="H42">
+        <v>1922</v>
+      </c>
+      <c r="I42">
+        <v>10205418</v>
+      </c>
+      <c r="J42">
+        <v>10934</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="1">
+        <v>2089</v>
+      </c>
+      <c r="E43">
+        <v>6281540</v>
+      </c>
+      <c r="F43">
+        <v>6730</v>
+      </c>
+      <c r="G43">
+        <v>598749</v>
+      </c>
+      <c r="H43">
+        <v>642</v>
+      </c>
+      <c r="I43">
+        <v>6880289</v>
+      </c>
+      <c r="J43">
+        <v>7372</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1199</v>
+      </c>
+      <c r="E44">
+        <v>3048890</v>
+      </c>
+      <c r="F44">
+        <v>3267</v>
+      </c>
+      <c r="G44">
+        <v>222582</v>
+      </c>
+      <c r="H44">
+        <v>238</v>
+      </c>
+      <c r="I44">
+        <v>3271472</v>
+      </c>
+      <c r="J44">
+        <v>3505</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1276</v>
+      </c>
+      <c r="E45">
+        <v>3225166</v>
+      </c>
+      <c r="F45">
+        <v>3456</v>
+      </c>
+      <c r="G45">
+        <v>412582</v>
+      </c>
+      <c r="H45">
+        <v>442</v>
+      </c>
+      <c r="I45">
+        <v>3637748</v>
+      </c>
+      <c r="J45">
+        <v>3898</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1286</v>
+      </c>
+      <c r="E46">
+        <v>4909584</v>
+      </c>
+      <c r="F46">
+        <v>5261</v>
+      </c>
+      <c r="G46">
+        <v>858915</v>
+      </c>
+      <c r="H46">
+        <v>920</v>
+      </c>
+      <c r="I46">
+        <v>5768499</v>
+      </c>
+      <c r="J46">
+        <v>6181</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47">
+        <v>384</v>
+      </c>
+      <c r="E47">
+        <v>1244367</v>
+      </c>
+      <c r="F47">
+        <v>1332</v>
+      </c>
+      <c r="G47">
+        <v>189573</v>
+      </c>
+      <c r="H47">
+        <v>204</v>
+      </c>
+      <c r="I47">
+        <v>1433940</v>
+      </c>
+      <c r="J47">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>34</v>
+      </c>
+      <c r="B48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49">
+        <v>256</v>
+      </c>
+      <c r="E49">
+        <v>809211</v>
+      </c>
+      <c r="F49">
+        <v>867</v>
+      </c>
+      <c r="G49">
+        <v>134216</v>
+      </c>
+      <c r="H49">
+        <v>144</v>
+      </c>
+      <c r="I49">
+        <v>943427</v>
+      </c>
+      <c r="J49">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50">
+        <v>408</v>
+      </c>
+      <c r="E50">
+        <v>1820284</v>
+      </c>
+      <c r="F50">
+        <v>1950</v>
+      </c>
+      <c r="G50">
+        <v>260100</v>
+      </c>
+      <c r="H50">
+        <v>279</v>
+      </c>
+      <c r="I50">
+        <v>2080384</v>
+      </c>
+      <c r="J50">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52">
+        <v>139</v>
+      </c>
+      <c r="E52">
+        <v>613340</v>
+      </c>
+      <c r="F52">
+        <v>658</v>
+      </c>
+      <c r="G52">
+        <v>92866</v>
+      </c>
+      <c r="H52">
+        <v>99</v>
+      </c>
+      <c r="I52">
+        <v>706206</v>
+      </c>
+      <c r="J52">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>34</v>
+      </c>
+      <c r="B53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53">
+        <v>128</v>
+      </c>
+      <c r="E53">
+        <v>506442</v>
+      </c>
+      <c r="F53">
+        <v>542</v>
+      </c>
+      <c r="G53">
+        <v>66847</v>
+      </c>
+      <c r="H53">
+        <v>72</v>
+      </c>
+      <c r="I53">
+        <v>573289</v>
+      </c>
+      <c r="J53">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>34</v>
+      </c>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" t="s">
+        <v>26</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>34</v>
+      </c>
+      <c r="B55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" s="1">
+        <v>4730</v>
+      </c>
+      <c r="E55">
+        <v>46171</v>
+      </c>
+      <c r="F55">
+        <v>12719</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>46171</v>
+      </c>
+      <c r="J55">
+        <v>12719</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>34</v>
+      </c>
+      <c r="B56" t="s">
+        <v>29</v>
+      </c>
+      <c r="C56" t="s">
+        <v>30</v>
+      </c>
+      <c r="D56" s="1">
+        <v>4277</v>
+      </c>
+      <c r="E56">
+        <v>14963</v>
+      </c>
+      <c r="F56">
+        <v>14963</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>14963</v>
+      </c>
+      <c r="J56">
+        <v>14963</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>34</v>
+      </c>
+      <c r="B57" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" t="s">
+        <v>31</v>
+      </c>
+      <c r="D57">
+        <v>577</v>
+      </c>
+      <c r="E57">
+        <v>7681</v>
+      </c>
+      <c r="F57">
+        <v>2116</v>
+      </c>
+      <c r="G57">
+        <v>1536</v>
+      </c>
+      <c r="H57">
+        <v>423</v>
+      </c>
+      <c r="I57">
+        <v>9217</v>
+      </c>
+      <c r="J57">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>34</v>
+      </c>
+      <c r="B58" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58">
+        <v>213</v>
+      </c>
+      <c r="E58">
+        <v>2075</v>
+      </c>
+      <c r="F58">
+        <v>572</v>
+      </c>
+      <c r="G58">
+        <v>330</v>
+      </c>
+      <c r="H58">
+        <v>91</v>
+      </c>
+      <c r="I58">
+        <v>2405</v>
+      </c>
+      <c r="J58">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" s="1">
+        <v>29277</v>
+      </c>
+      <c r="E59">
+        <v>126228234</v>
+      </c>
+      <c r="F59">
+        <v>135730</v>
+      </c>
+      <c r="G59">
+        <v>11855360</v>
+      </c>
+      <c r="H59">
+        <v>12747</v>
+      </c>
+      <c r="I59">
+        <v>138083594</v>
+      </c>
+      <c r="J59">
+        <v>148477</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>35</v>
+      </c>
+      <c r="B60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="1">
+        <v>23068</v>
+      </c>
+      <c r="E60">
+        <v>90188037</v>
+      </c>
+      <c r="F60">
+        <v>96976</v>
+      </c>
+      <c r="G60">
+        <v>15411731</v>
+      </c>
+      <c r="H60">
+        <v>16572</v>
+      </c>
+      <c r="I60">
+        <v>105599768</v>
+      </c>
+      <c r="J60">
+        <v>113548</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61">
+        <v>873</v>
+      </c>
+      <c r="E61">
+        <v>2798716</v>
+      </c>
+      <c r="F61">
+        <v>3009</v>
+      </c>
+      <c r="G61">
+        <v>596608</v>
+      </c>
+      <c r="H61">
+        <v>642</v>
+      </c>
+      <c r="I61">
+        <v>3395324</v>
+      </c>
+      <c r="J61">
+        <v>3651</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="B62" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="1">
+        <v>2370</v>
+      </c>
+      <c r="E62">
+        <v>7126496</v>
+      </c>
+      <c r="F62">
+        <v>7663</v>
+      </c>
+      <c r="G62">
+        <v>679289</v>
+      </c>
+      <c r="H62">
+        <v>730</v>
+      </c>
+      <c r="I62">
+        <v>7805785</v>
+      </c>
+      <c r="J62">
+        <v>8393</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>35</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
+        <v>16</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1302</v>
+      </c>
+      <c r="E63">
+        <v>3310804</v>
+      </c>
+      <c r="F63">
+        <v>3560</v>
+      </c>
+      <c r="G63">
+        <v>241703</v>
+      </c>
+      <c r="H63">
+        <v>260</v>
+      </c>
+      <c r="I63">
+        <v>3552507</v>
+      </c>
+      <c r="J63">
+        <v>3820</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1812</v>
+      </c>
+      <c r="E64">
+        <v>4579939</v>
+      </c>
+      <c r="F64">
+        <v>4925</v>
+      </c>
+      <c r="G64">
+        <v>585892</v>
+      </c>
+      <c r="H64">
+        <v>630</v>
+      </c>
+      <c r="I64">
+        <v>5165831</v>
+      </c>
+      <c r="J64">
+        <v>5555</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>35</v>
+      </c>
+      <c r="B65" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1015</v>
+      </c>
+      <c r="E65">
+        <v>3877165</v>
+      </c>
+      <c r="F65">
+        <v>4169</v>
+      </c>
+      <c r="G65">
+        <v>678297</v>
+      </c>
+      <c r="H65">
+        <v>729</v>
+      </c>
+      <c r="I65">
+        <v>4555462</v>
+      </c>
+      <c r="J65">
+        <v>4898</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>35</v>
+      </c>
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66">
+        <v>246</v>
+      </c>
+      <c r="E66">
+        <v>797172</v>
+      </c>
+      <c r="F66">
+        <v>857</v>
+      </c>
+      <c r="G66">
+        <v>121446</v>
+      </c>
+      <c r="H66">
+        <v>131</v>
+      </c>
+      <c r="I66">
+        <v>918618</v>
+      </c>
+      <c r="J66">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>35</v>
+      </c>
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>35</v>
+      </c>
+      <c r="B68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" t="s">
+        <v>21</v>
+      </c>
+      <c r="D68">
+        <v>226</v>
+      </c>
+      <c r="E68">
+        <v>714382</v>
+      </c>
+      <c r="F68">
+        <v>769</v>
+      </c>
+      <c r="G68">
+        <v>118487</v>
+      </c>
+      <c r="H68">
+        <v>127</v>
+      </c>
+      <c r="I68">
+        <v>832869</v>
+      </c>
+      <c r="J68">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>35</v>
+      </c>
+      <c r="B69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" t="s">
+        <v>22</v>
+      </c>
+      <c r="D69">
+        <v>480</v>
+      </c>
+      <c r="E69">
+        <v>2141510</v>
+      </c>
+      <c r="F69">
+        <v>2303</v>
+      </c>
+      <c r="G69">
+        <v>306000</v>
+      </c>
+      <c r="H69">
+        <v>329</v>
+      </c>
+      <c r="I69">
+        <v>2447510</v>
+      </c>
+      <c r="J69">
+        <v>2632</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>35</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" t="s">
+        <v>23</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>35</v>
+      </c>
+      <c r="B71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" t="s">
+        <v>24</v>
+      </c>
+      <c r="D71">
+        <v>152</v>
+      </c>
+      <c r="E71">
+        <v>670703</v>
+      </c>
+      <c r="F71">
+        <v>721</v>
+      </c>
+      <c r="G71">
+        <v>101551</v>
+      </c>
+      <c r="H71">
+        <v>109</v>
+      </c>
+      <c r="I71">
+        <v>772254</v>
+      </c>
+      <c r="J71">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>35</v>
+      </c>
+      <c r="B72" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>25</v>
+      </c>
+      <c r="D72">
+        <v>224</v>
+      </c>
+      <c r="E72">
+        <v>886274</v>
+      </c>
+      <c r="F72">
+        <v>953</v>
+      </c>
+      <c r="G72">
+        <v>116982</v>
+      </c>
+      <c r="H72">
+        <v>126</v>
+      </c>
+      <c r="I72">
+        <v>1003256</v>
+      </c>
+      <c r="J72">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>35</v>
+      </c>
+      <c r="B73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" t="s">
+        <v>26</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>35</v>
+      </c>
+      <c r="B74" t="s">
+        <v>27</v>
+      </c>
+      <c r="C74" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" s="1">
+        <v>6540</v>
+      </c>
+      <c r="E74">
+        <v>63842</v>
+      </c>
+      <c r="F74">
+        <v>17491</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>63842</v>
+      </c>
+      <c r="J74">
+        <v>17491</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>35</v>
+      </c>
+      <c r="B75" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" s="1">
+        <v>4201</v>
+      </c>
+      <c r="E75">
+        <v>14696</v>
+      </c>
+      <c r="F75">
+        <v>14696</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>14696</v>
+      </c>
+      <c r="J75">
+        <v>14696</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>35</v>
+      </c>
+      <c r="B76" t="s">
+        <v>27</v>
+      </c>
+      <c r="C76" t="s">
+        <v>31</v>
+      </c>
+      <c r="D76">
+        <v>150</v>
+      </c>
+      <c r="E76">
+        <v>1997</v>
+      </c>
+      <c r="F76">
+        <v>547</v>
+      </c>
+      <c r="G76">
+        <v>399</v>
+      </c>
+      <c r="H76">
+        <v>109</v>
+      </c>
+      <c r="I76">
+        <v>2396</v>
+      </c>
+      <c r="J76">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>35</v>
+      </c>
+      <c r="B77" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77" t="s">
+        <v>32</v>
+      </c>
+      <c r="D77">
+        <v>270</v>
+      </c>
+      <c r="E77">
+        <v>2630</v>
+      </c>
+      <c r="F77">
+        <v>720</v>
+      </c>
+      <c r="G77">
+        <v>419</v>
+      </c>
+      <c r="H77">
+        <v>115</v>
+      </c>
+      <c r="I77">
+        <v>3049</v>
+      </c>
+      <c r="J77">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>43</v>
+      </c>
+      <c r="B78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" s="1">
+        <v>18384</v>
+      </c>
+      <c r="E78">
+        <v>79263208</v>
+      </c>
+      <c r="F78">
+        <v>85229</v>
+      </c>
+      <c r="G78">
+        <v>7444403</v>
+      </c>
+      <c r="H78">
+        <v>8005</v>
+      </c>
+      <c r="I78">
+        <v>86707611</v>
+      </c>
+      <c r="J78">
+        <v>93234</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>43</v>
+      </c>
+      <c r="B79" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="1">
+        <v>25216</v>
+      </c>
+      <c r="E79">
+        <v>98585986</v>
+      </c>
+      <c r="F79">
+        <v>106007</v>
+      </c>
+      <c r="G79">
+        <v>16846810</v>
+      </c>
+      <c r="H79">
+        <v>18114</v>
+      </c>
+      <c r="I79">
+        <v>115432796</v>
+      </c>
+      <c r="J79">
+        <v>124121</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>43</v>
+      </c>
+      <c r="B80" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>43</v>
+      </c>
+      <c r="B81" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="1">
+        <v>1993</v>
+      </c>
+      <c r="E81">
+        <v>5992871</v>
+      </c>
+      <c r="F81">
+        <v>6444</v>
+      </c>
+      <c r="G81">
+        <v>571234</v>
+      </c>
+      <c r="H81">
+        <v>614</v>
+      </c>
+      <c r="I81">
+        <v>6564105</v>
+      </c>
+      <c r="J81">
+        <v>7058</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>43</v>
+      </c>
+      <c r="B82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" t="s">
+        <v>16</v>
+      </c>
+      <c r="D82" s="1">
+        <v>1318</v>
+      </c>
+      <c r="E82">
+        <v>3351489</v>
+      </c>
+      <c r="F82">
+        <v>3604</v>
+      </c>
+      <c r="G82">
+        <v>244674</v>
+      </c>
+      <c r="H82">
+        <v>263</v>
+      </c>
+      <c r="I82">
+        <v>3596163</v>
+      </c>
+      <c r="J82">
+        <v>3867</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>43</v>
+      </c>
+      <c r="B83" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83">
+        <v>770</v>
+      </c>
+      <c r="E83">
+        <v>1946221</v>
+      </c>
+      <c r="F83">
+        <v>2092</v>
+      </c>
+      <c r="G83">
+        <v>248972</v>
+      </c>
+      <c r="H83">
+        <v>268</v>
+      </c>
+      <c r="I83">
+        <v>2195193</v>
+      </c>
+      <c r="J83">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>43</v>
+      </c>
+      <c r="B84" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" t="s">
+        <v>18</v>
+      </c>
+      <c r="D84">
+        <v>676</v>
+      </c>
+      <c r="E84">
+        <v>2580633</v>
+      </c>
+      <c r="F84">
+        <v>2775</v>
+      </c>
+      <c r="G84">
+        <v>451473</v>
+      </c>
+      <c r="H84">
+        <v>485</v>
+      </c>
+      <c r="I84">
+        <v>3032106</v>
+      </c>
+      <c r="J84">
+        <v>3260</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>43</v>
+      </c>
+      <c r="B85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" t="s">
+        <v>19</v>
+      </c>
+      <c r="D85">
+        <v>324</v>
+      </c>
+      <c r="E85">
+        <v>1049934</v>
+      </c>
+      <c r="F85">
+        <v>1129</v>
+      </c>
+      <c r="G85">
+        <v>159953</v>
+      </c>
+      <c r="H85">
+        <v>172</v>
+      </c>
+      <c r="I85">
+        <v>1209887</v>
+      </c>
+      <c r="J85">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>43</v>
+      </c>
+      <c r="B86" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" t="s">
+        <v>20</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>43</v>
+      </c>
+      <c r="B87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87">
+        <v>291</v>
+      </c>
+      <c r="E87">
+        <v>919846</v>
+      </c>
+      <c r="F87">
+        <v>989</v>
+      </c>
+      <c r="G87">
+        <v>152565</v>
+      </c>
+      <c r="H87">
+        <v>164</v>
+      </c>
+      <c r="I87">
+        <v>1072411</v>
+      </c>
+      <c r="J87">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>43</v>
+      </c>
+      <c r="B88" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" t="s">
+        <v>22</v>
+      </c>
+      <c r="D88">
+        <v>436</v>
+      </c>
+      <c r="E88">
+        <v>1945205</v>
+      </c>
+      <c r="F88">
+        <v>2091</v>
+      </c>
+      <c r="G88">
+        <v>277950</v>
+      </c>
+      <c r="H88">
+        <v>299</v>
+      </c>
+      <c r="I88">
+        <v>2223155</v>
+      </c>
+      <c r="J88">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>43</v>
+      </c>
+      <c r="B89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" t="s">
+        <v>23</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>43</v>
+      </c>
+      <c r="B90" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" t="s">
+        <v>24</v>
+      </c>
+      <c r="D90">
+        <v>177</v>
+      </c>
+      <c r="E90">
+        <v>781016</v>
+      </c>
+      <c r="F90">
+        <v>840</v>
+      </c>
+      <c r="G90">
+        <v>118254</v>
+      </c>
+      <c r="H90">
+        <v>127</v>
+      </c>
+      <c r="I90">
+        <v>899270</v>
+      </c>
+      <c r="J90">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>43</v>
+      </c>
+      <c r="B91" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" t="s">
+        <v>25</v>
+      </c>
+      <c r="D91">
+        <v>168</v>
+      </c>
+      <c r="E91">
+        <v>664706</v>
+      </c>
+      <c r="F91">
+        <v>715</v>
+      </c>
+      <c r="G91">
+        <v>87736</v>
+      </c>
+      <c r="H91">
+        <v>94</v>
+      </c>
+      <c r="I91">
+        <v>752442</v>
+      </c>
+      <c r="J91">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>43</v>
+      </c>
+      <c r="B92" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" t="s">
+        <v>26</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>43</v>
+      </c>
+      <c r="B93" t="s">
+        <v>27</v>
+      </c>
+      <c r="C93" t="s">
+        <v>28</v>
+      </c>
+      <c r="D93" s="1">
+        <v>11727</v>
+      </c>
+      <c r="E93">
+        <v>114475</v>
+      </c>
+      <c r="F93">
+        <v>31107</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>114475</v>
+      </c>
+      <c r="J93">
+        <v>31107</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>43</v>
+      </c>
+      <c r="B94" t="s">
+        <v>29</v>
+      </c>
+      <c r="C94" t="s">
+        <v>30</v>
+      </c>
+      <c r="D94" s="1">
+        <v>3210</v>
+      </c>
+      <c r="E94">
+        <v>11229</v>
+      </c>
+      <c r="F94">
+        <v>11229</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>11229</v>
+      </c>
+      <c r="J94">
+        <v>11229</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>43</v>
+      </c>
+      <c r="B95" t="s">
+        <v>27</v>
+      </c>
+      <c r="C95" t="s">
+        <v>31</v>
+      </c>
+      <c r="D95">
+        <v>285</v>
+      </c>
+      <c r="E95">
+        <v>3793</v>
+      </c>
+      <c r="F95">
+        <v>1031</v>
+      </c>
+      <c r="G95">
+        <v>759</v>
+      </c>
+      <c r="H95">
+        <v>206</v>
+      </c>
+      <c r="I95">
+        <v>4552</v>
+      </c>
+      <c r="J95">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>43</v>
+      </c>
+      <c r="B96" t="s">
+        <v>27</v>
+      </c>
+      <c r="C96" t="s">
+        <v>32</v>
+      </c>
+      <c r="D96">
+        <v>152</v>
+      </c>
+      <c r="E96">
+        <v>1480</v>
+      </c>
+      <c r="F96">
+        <v>402</v>
+      </c>
+      <c r="G96">
+        <v>236</v>
+      </c>
+      <c r="H96">
+        <v>64</v>
+      </c>
+      <c r="I96">
+        <v>1716</v>
+      </c>
+      <c r="J96">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>42</v>
+      </c>
+      <c r="B97" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" t="s">
+        <v>12</v>
+      </c>
+      <c r="D97" s="1">
+        <v>36594</v>
+      </c>
+      <c r="E97">
+        <v>157778649</v>
+      </c>
+      <c r="F97">
+        <v>169654</v>
+      </c>
+      <c r="G97">
+        <v>14818577</v>
+      </c>
+      <c r="H97">
+        <v>15934</v>
+      </c>
+      <c r="I97">
+        <v>172597226</v>
+      </c>
+      <c r="J97">
+        <v>185588</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>42</v>
+      </c>
+      <c r="B98" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" t="s">
+        <v>13</v>
+      </c>
+      <c r="D98" s="1">
+        <v>43390</v>
+      </c>
+      <c r="E98">
+        <v>169641712</v>
+      </c>
+      <c r="F98">
+        <v>182411</v>
+      </c>
+      <c r="G98">
+        <v>28989126</v>
+      </c>
+      <c r="H98">
+        <v>31171</v>
+      </c>
+      <c r="I98">
+        <v>198630838</v>
+      </c>
+      <c r="J98">
+        <v>213582</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>42</v>
+      </c>
+      <c r="B99" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>42</v>
+      </c>
+      <c r="B100" t="s">
+        <v>11</v>
+      </c>
+      <c r="C100" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" s="1">
+        <v>8370</v>
+      </c>
+      <c r="E100">
+        <v>25168256</v>
+      </c>
+      <c r="F100">
+        <v>27062</v>
+      </c>
+      <c r="G100">
+        <v>2399009</v>
+      </c>
+      <c r="H100">
+        <v>2580</v>
+      </c>
+      <c r="I100">
+        <v>27567265</v>
+      </c>
+      <c r="J100">
+        <v>29642</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>42</v>
+      </c>
+      <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" t="s">
+        <v>16</v>
+      </c>
+      <c r="D101" s="1">
+        <v>3424</v>
+      </c>
+      <c r="E101">
+        <v>8706753</v>
+      </c>
+      <c r="F101">
+        <v>9363</v>
+      </c>
+      <c r="G101">
+        <v>635631</v>
+      </c>
+      <c r="H101">
+        <v>683</v>
+      </c>
+      <c r="I101">
+        <v>9342384</v>
+      </c>
+      <c r="J101">
+        <v>10046</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>42</v>
+      </c>
+      <c r="B102" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" t="s">
+        <v>17</v>
+      </c>
+      <c r="D102" s="1">
+        <v>2563</v>
+      </c>
+      <c r="E102">
+        <v>6478137</v>
+      </c>
+      <c r="F102">
+        <v>6966</v>
+      </c>
+      <c r="G102">
+        <v>828720</v>
+      </c>
+      <c r="H102">
+        <v>891</v>
+      </c>
+      <c r="I102">
+        <v>7306857</v>
+      </c>
+      <c r="J102">
+        <v>7857</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>42</v>
+      </c>
+      <c r="B103" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103" t="s">
+        <v>18</v>
+      </c>
+      <c r="D103" s="1">
+        <v>1455</v>
+      </c>
+      <c r="E103">
+        <v>5558144</v>
+      </c>
+      <c r="F103">
+        <v>5976</v>
+      </c>
+      <c r="G103">
+        <v>972378</v>
+      </c>
+      <c r="H103">
+        <v>1046</v>
+      </c>
+      <c r="I103">
+        <v>6530522</v>
+      </c>
+      <c r="J103">
+        <v>7022</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>42</v>
+      </c>
+      <c r="B104" t="s">
+        <v>11</v>
+      </c>
+      <c r="C104" t="s">
+        <v>19</v>
+      </c>
+      <c r="D104" s="1">
+        <v>1004</v>
+      </c>
+      <c r="E104">
+        <v>3253503</v>
+      </c>
+      <c r="F104">
+        <v>3498</v>
+      </c>
+      <c r="G104">
+        <v>495654</v>
+      </c>
+      <c r="H104">
+        <v>533</v>
+      </c>
+      <c r="I104">
+        <v>3749157</v>
+      </c>
+      <c r="J104">
+        <v>4031</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>42</v>
+      </c>
+      <c r="B105" t="s">
+        <v>11</v>
+      </c>
+      <c r="C105" t="s">
+        <v>20</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>42</v>
+      </c>
+      <c r="B106" t="s">
+        <v>11</v>
+      </c>
+      <c r="C106" t="s">
+        <v>21</v>
+      </c>
+      <c r="D106">
+        <v>312</v>
+      </c>
+      <c r="E106">
+        <v>986226</v>
+      </c>
+      <c r="F106">
+        <v>1060</v>
+      </c>
+      <c r="G106">
+        <v>163575</v>
+      </c>
+      <c r="H106">
+        <v>176</v>
+      </c>
+      <c r="I106">
+        <v>1149801</v>
+      </c>
+      <c r="J106">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>42</v>
+      </c>
+      <c r="B107" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107" t="s">
+        <v>22</v>
+      </c>
+      <c r="D107">
+        <v>491</v>
+      </c>
+      <c r="E107">
+        <v>2190586</v>
+      </c>
+      <c r="F107">
+        <v>2355</v>
+      </c>
+      <c r="G107">
+        <v>313013</v>
+      </c>
+      <c r="H107">
+        <v>337</v>
+      </c>
+      <c r="I107">
+        <v>2503599</v>
+      </c>
+      <c r="J107">
+        <v>2692</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>42</v>
+      </c>
+      <c r="B108" t="s">
+        <v>11</v>
+      </c>
+      <c r="C108" t="s">
+        <v>23</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>42</v>
+      </c>
+      <c r="B109" t="s">
+        <v>11</v>
+      </c>
+      <c r="C109" t="s">
+        <v>24</v>
+      </c>
+      <c r="D109">
+        <v>303</v>
+      </c>
+      <c r="E109">
+        <v>1336994</v>
+      </c>
+      <c r="F109">
+        <v>1437</v>
+      </c>
+      <c r="G109">
+        <v>202434</v>
+      </c>
+      <c r="H109">
+        <v>218</v>
+      </c>
+      <c r="I109">
+        <v>1539428</v>
+      </c>
+      <c r="J109">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>42</v>
+      </c>
+      <c r="B110" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110" t="s">
+        <v>25</v>
+      </c>
+      <c r="D110">
+        <v>116</v>
+      </c>
+      <c r="E110">
+        <v>458963</v>
+      </c>
+      <c r="F110">
+        <v>494</v>
+      </c>
+      <c r="G110">
+        <v>60580</v>
+      </c>
+      <c r="H110">
+        <v>65</v>
+      </c>
+      <c r="I110">
+        <v>519543</v>
+      </c>
+      <c r="J110">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>42</v>
+      </c>
+      <c r="B111" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" t="s">
+        <v>26</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>42</v>
+      </c>
+      <c r="B112" t="s">
+        <v>27</v>
+      </c>
+      <c r="C112" t="s">
+        <v>28</v>
+      </c>
+      <c r="D112" s="1">
+        <v>15588</v>
+      </c>
+      <c r="E112">
+        <v>152164</v>
+      </c>
+      <c r="F112">
+        <v>41125</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>152164</v>
+      </c>
+      <c r="J112">
+        <v>41125</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>42</v>
+      </c>
+      <c r="B113" t="s">
+        <v>29</v>
+      </c>
+      <c r="C113" t="s">
+        <v>30</v>
+      </c>
+      <c r="D113" s="1">
+        <v>4516</v>
+      </c>
+      <c r="E113">
+        <v>15800</v>
+      </c>
+      <c r="F113">
+        <v>15800</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>15800</v>
+      </c>
+      <c r="J113">
+        <v>15800</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>42</v>
+      </c>
+      <c r="B114" t="s">
+        <v>27</v>
+      </c>
+      <c r="C114" t="s">
+        <v>31</v>
+      </c>
+      <c r="D114" s="1">
+        <v>1193</v>
+      </c>
+      <c r="E114">
+        <v>15880</v>
+      </c>
+      <c r="F114">
+        <v>4292</v>
+      </c>
+      <c r="G114">
+        <v>3176</v>
+      </c>
+      <c r="H114">
+        <v>858</v>
+      </c>
+      <c r="I114">
+        <v>19056</v>
+      </c>
+      <c r="J114">
+        <v>5150</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>42</v>
+      </c>
+      <c r="B115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C115" t="s">
+        <v>32</v>
+      </c>
+      <c r="D115">
+        <v>132</v>
+      </c>
+      <c r="E115">
+        <v>1285</v>
+      </c>
+      <c r="F115">
+        <v>348</v>
+      </c>
+      <c r="G115">
+        <v>205</v>
+      </c>
+      <c r="H115">
+        <v>55</v>
+      </c>
+      <c r="I115">
+        <v>1490</v>
+      </c>
+      <c r="J115">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>41</v>
+      </c>
+      <c r="B116" t="s">
+        <v>11</v>
+      </c>
+      <c r="C116" t="s">
+        <v>12</v>
+      </c>
+      <c r="D116" s="1">
+        <v>30813</v>
+      </c>
+      <c r="E116">
+        <v>132851848</v>
+      </c>
+      <c r="F116">
+        <v>143109</v>
+      </c>
+      <c r="G116">
+        <v>12477450</v>
+      </c>
+      <c r="H116">
+        <v>13440</v>
+      </c>
+      <c r="I116">
+        <v>145329298</v>
+      </c>
+      <c r="J116">
+        <v>156549</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>41</v>
+      </c>
+      <c r="B117" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" s="1">
+        <v>26255</v>
+      </c>
+      <c r="E117">
+        <v>102649509</v>
+      </c>
+      <c r="F117">
+        <v>110575</v>
+      </c>
+      <c r="G117">
+        <v>17541202</v>
+      </c>
+      <c r="H117">
+        <v>18895</v>
+      </c>
+      <c r="I117">
+        <v>120190711</v>
+      </c>
+      <c r="J117">
+        <v>129470</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>41</v>
+      </c>
+      <c r="B118" t="s">
+        <v>11</v>
+      </c>
+      <c r="C118" t="s">
+        <v>14</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>41</v>
+      </c>
+      <c r="B119" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119" t="s">
+        <v>15</v>
+      </c>
+      <c r="D119" s="1">
+        <v>3194</v>
+      </c>
+      <c r="E119">
+        <v>9604231</v>
+      </c>
+      <c r="F119">
+        <v>10346</v>
+      </c>
+      <c r="G119">
+        <v>915464</v>
+      </c>
+      <c r="H119">
+        <v>986</v>
+      </c>
+      <c r="I119">
+        <v>10519695</v>
+      </c>
+      <c r="J119">
+        <v>11332</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>41</v>
+      </c>
+      <c r="B120" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120" t="s">
+        <v>16</v>
+      </c>
+      <c r="D120" s="1">
+        <v>1342</v>
+      </c>
+      <c r="E120">
+        <v>3412518</v>
+      </c>
+      <c r="F120">
+        <v>3676</v>
+      </c>
+      <c r="G120">
+        <v>249129</v>
+      </c>
+      <c r="H120">
+        <v>268</v>
+      </c>
+      <c r="I120">
+        <v>3661647</v>
+      </c>
+      <c r="J120">
+        <v>3944</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>41</v>
+      </c>
+      <c r="B121" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121" t="s">
+        <v>17</v>
+      </c>
+      <c r="D121" s="1">
+        <v>1113</v>
+      </c>
+      <c r="E121">
+        <v>2813175</v>
+      </c>
+      <c r="F121">
+        <v>3030</v>
+      </c>
+      <c r="G121">
+        <v>359877</v>
+      </c>
+      <c r="H121">
+        <v>388</v>
+      </c>
+      <c r="I121">
+        <v>3173052</v>
+      </c>
+      <c r="J121">
+        <v>3418</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>41</v>
+      </c>
+      <c r="B122" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" t="s">
+        <v>18</v>
+      </c>
+      <c r="D122">
+        <v>691</v>
+      </c>
+      <c r="E122">
+        <v>2638083</v>
+      </c>
+      <c r="F122">
+        <v>2842</v>
+      </c>
+      <c r="G122">
+        <v>461523</v>
+      </c>
+      <c r="H122">
+        <v>497</v>
+      </c>
+      <c r="I122">
+        <v>3099606</v>
+      </c>
+      <c r="J122">
+        <v>3339</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>41</v>
+      </c>
+      <c r="B123" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123" t="s">
+        <v>19</v>
+      </c>
+      <c r="D123">
+        <v>269</v>
+      </c>
+      <c r="E123">
+        <v>871705</v>
+      </c>
+      <c r="F123">
+        <v>939</v>
+      </c>
+      <c r="G123">
+        <v>132800</v>
+      </c>
+      <c r="H123">
+        <v>143</v>
+      </c>
+      <c r="I123">
+        <v>1004505</v>
+      </c>
+      <c r="J123">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>41</v>
+      </c>
+      <c r="B124" t="s">
+        <v>11</v>
+      </c>
+      <c r="C124" t="s">
+        <v>20</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>41</v>
+      </c>
+      <c r="B125" t="s">
+        <v>11</v>
+      </c>
+      <c r="C125" t="s">
+        <v>21</v>
+      </c>
+      <c r="D125">
+        <v>389</v>
+      </c>
+      <c r="E125">
+        <v>1229621</v>
+      </c>
+      <c r="F125">
+        <v>1324</v>
+      </c>
+      <c r="G125">
+        <v>203945</v>
+      </c>
+      <c r="H125">
+        <v>220</v>
+      </c>
+      <c r="I125">
+        <v>1433566</v>
+      </c>
+      <c r="J125">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>41</v>
+      </c>
+      <c r="B126" t="s">
+        <v>11</v>
+      </c>
+      <c r="C126" t="s">
+        <v>22</v>
+      </c>
+      <c r="D126">
+        <v>448</v>
+      </c>
+      <c r="E126">
+        <v>1998743</v>
+      </c>
+      <c r="F126">
+        <v>2153</v>
+      </c>
+      <c r="G126">
+        <v>285600</v>
+      </c>
+      <c r="H126">
+        <v>308</v>
+      </c>
+      <c r="I126">
+        <v>2284343</v>
+      </c>
+      <c r="J126">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>41</v>
+      </c>
+      <c r="B127" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127" t="s">
+        <v>23</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>41</v>
+      </c>
+      <c r="B128" t="s">
+        <v>11</v>
+      </c>
+      <c r="C128" t="s">
+        <v>24</v>
+      </c>
+      <c r="D128">
+        <v>148</v>
+      </c>
+      <c r="E128">
+        <v>653053</v>
+      </c>
+      <c r="F128">
+        <v>703</v>
+      </c>
+      <c r="G128">
+        <v>98879</v>
+      </c>
+      <c r="H128">
+        <v>107</v>
+      </c>
+      <c r="I128">
+        <v>751932</v>
+      </c>
+      <c r="J128">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>41</v>
+      </c>
+      <c r="B129" t="s">
+        <v>11</v>
+      </c>
+      <c r="C129" t="s">
+        <v>25</v>
+      </c>
+      <c r="D129">
+        <v>187</v>
+      </c>
+      <c r="E129">
+        <v>739880</v>
+      </c>
+      <c r="F129">
+        <v>797</v>
+      </c>
+      <c r="G129">
+        <v>97659</v>
+      </c>
+      <c r="H129">
+        <v>105</v>
+      </c>
+      <c r="I129">
+        <v>837539</v>
+      </c>
+      <c r="J129">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>41</v>
+      </c>
+      <c r="B130" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" t="s">
+        <v>26</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+      <c r="E130">
+        <v>0</v>
+      </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>41</v>
+      </c>
+      <c r="B131" t="s">
+        <v>27</v>
+      </c>
+      <c r="C131" t="s">
+        <v>28</v>
+      </c>
+      <c r="D131" s="1">
+        <v>18516</v>
+      </c>
+      <c r="E131">
+        <v>180741</v>
+      </c>
+      <c r="F131">
+        <v>48849</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>180741</v>
+      </c>
+      <c r="J131">
+        <v>48849</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>41</v>
+      </c>
+      <c r="B132" t="s">
+        <v>29</v>
+      </c>
+      <c r="C132" t="s">
+        <v>30</v>
+      </c>
+      <c r="D132" s="1">
+        <v>4458</v>
+      </c>
+      <c r="E132">
+        <v>15596</v>
+      </c>
+      <c r="F132">
+        <v>15596</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>15596</v>
+      </c>
+      <c r="J132">
+        <v>15596</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>41</v>
+      </c>
+      <c r="B133" t="s">
+        <v>27</v>
+      </c>
+      <c r="C133" t="s">
+        <v>31</v>
+      </c>
+      <c r="D133">
+        <v>985</v>
+      </c>
+      <c r="E133">
+        <v>13112</v>
+      </c>
+      <c r="F133">
+        <v>3543</v>
+      </c>
+      <c r="G133">
+        <v>2622</v>
+      </c>
+      <c r="H133">
+        <v>709</v>
+      </c>
+      <c r="I133">
+        <v>15734</v>
+      </c>
+      <c r="J133">
+        <v>4252</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>41</v>
+      </c>
+      <c r="B134" t="s">
+        <v>27</v>
+      </c>
+      <c r="C134" t="s">
+        <v>32</v>
+      </c>
+      <c r="D134">
+        <v>437</v>
+      </c>
+      <c r="E134">
+        <v>4256</v>
+      </c>
+      <c r="F134">
+        <v>1151</v>
+      </c>
+      <c r="G134">
+        <v>678</v>
+      </c>
+      <c r="H134">
+        <v>183</v>
+      </c>
+      <c r="I134">
+        <v>4934</v>
+      </c>
+      <c r="J134">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>40</v>
+      </c>
+      <c r="B135" t="s">
+        <v>11</v>
+      </c>
+      <c r="C135" t="s">
+        <v>12</v>
+      </c>
+      <c r="D135" s="1">
+        <v>27820</v>
+      </c>
+      <c r="E135">
+        <v>119946239</v>
+      </c>
+      <c r="F135">
+        <v>129438</v>
+      </c>
+      <c r="G135">
+        <v>11265355</v>
+      </c>
+      <c r="H135">
+        <v>12157</v>
+      </c>
+      <c r="I135">
+        <v>131211594</v>
+      </c>
+      <c r="J135">
+        <v>141595</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>40</v>
+      </c>
+      <c r="B136" t="s">
+        <v>11</v>
+      </c>
+      <c r="C136" t="s">
+        <v>13</v>
+      </c>
+      <c r="D136" s="1">
+        <v>28995</v>
+      </c>
+      <c r="E136">
+        <v>113361374</v>
+      </c>
+      <c r="F136">
+        <v>122332</v>
+      </c>
+      <c r="G136">
+        <v>19371693</v>
+      </c>
+      <c r="H136">
+        <v>20905</v>
+      </c>
+      <c r="I136">
+        <v>132733067</v>
+      </c>
+      <c r="J136">
+        <v>143237</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>40</v>
+      </c>
+      <c r="B137" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" t="s">
+        <v>14</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="E137">
+        <v>0</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>40</v>
+      </c>
+      <c r="B138" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" t="s">
+        <v>15</v>
+      </c>
+      <c r="D138" s="1">
+        <v>2738</v>
+      </c>
+      <c r="E138">
+        <v>8233056</v>
+      </c>
+      <c r="F138">
+        <v>8884</v>
+      </c>
+      <c r="G138">
+        <v>784766</v>
+      </c>
+      <c r="H138">
+        <v>847</v>
+      </c>
+      <c r="I138">
+        <v>9017822</v>
+      </c>
+      <c r="J138">
+        <v>9731</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>40</v>
+      </c>
+      <c r="B139" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139" t="s">
+        <v>16</v>
+      </c>
+      <c r="D139" s="1">
+        <v>1216</v>
+      </c>
+      <c r="E139">
+        <v>3092118</v>
+      </c>
+      <c r="F139">
+        <v>3336</v>
+      </c>
+      <c r="G139">
+        <v>225738</v>
+      </c>
+      <c r="H139">
+        <v>244</v>
+      </c>
+      <c r="I139">
+        <v>3317856</v>
+      </c>
+      <c r="J139">
+        <v>3580</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>40</v>
+      </c>
+      <c r="B140" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" t="s">
+        <v>17</v>
+      </c>
+      <c r="D140">
+        <v>933</v>
+      </c>
+      <c r="E140">
+        <v>2358214</v>
+      </c>
+      <c r="F140">
+        <v>2544</v>
+      </c>
+      <c r="G140">
+        <v>301676</v>
+      </c>
+      <c r="H140">
+        <v>326</v>
+      </c>
+      <c r="I140">
+        <v>2659890</v>
+      </c>
+      <c r="J140">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>40</v>
+      </c>
+      <c r="B141" t="s">
+        <v>11</v>
+      </c>
+      <c r="C141" t="s">
+        <v>18</v>
+      </c>
+      <c r="D141">
+        <v>580</v>
+      </c>
+      <c r="E141">
+        <v>2213804</v>
+      </c>
+      <c r="F141">
+        <v>2389</v>
+      </c>
+      <c r="G141">
+        <v>387298</v>
+      </c>
+      <c r="H141">
+        <v>418</v>
+      </c>
+      <c r="I141">
+        <v>2601102</v>
+      </c>
+      <c r="J141">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>40</v>
+      </c>
+      <c r="B142" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142" t="s">
+        <v>19</v>
+      </c>
+      <c r="D142">
+        <v>542</v>
+      </c>
+      <c r="E142">
+        <v>1756373</v>
+      </c>
+      <c r="F142">
+        <v>1895</v>
+      </c>
+      <c r="G142">
+        <v>267574</v>
+      </c>
+      <c r="H142">
+        <v>289</v>
+      </c>
+      <c r="I142">
+        <v>2023947</v>
+      </c>
+      <c r="J142">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>40</v>
+      </c>
+      <c r="B143" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>40</v>
+      </c>
+      <c r="B144" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" t="s">
+        <v>21</v>
+      </c>
+      <c r="D144">
+        <v>370</v>
+      </c>
+      <c r="E144">
+        <v>1169562</v>
+      </c>
+      <c r="F144">
+        <v>1262</v>
+      </c>
+      <c r="G144">
+        <v>193984</v>
+      </c>
+      <c r="H144">
+        <v>209</v>
+      </c>
+      <c r="I144">
+        <v>1363546</v>
+      </c>
+      <c r="J144">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>40</v>
+      </c>
+      <c r="B145" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145" t="s">
+        <v>22</v>
+      </c>
+      <c r="D145">
+        <v>363</v>
+      </c>
+      <c r="E145">
+        <v>1619517</v>
+      </c>
+      <c r="F145">
+        <v>1747</v>
+      </c>
+      <c r="G145">
+        <v>231413</v>
+      </c>
+      <c r="H145">
+        <v>250</v>
+      </c>
+      <c r="I145">
+        <v>1850930</v>
+      </c>
+      <c r="J145">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>40</v>
+      </c>
+      <c r="B146" t="s">
+        <v>11</v>
+      </c>
+      <c r="C146" t="s">
+        <v>23</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="E146">
+        <v>0</v>
+      </c>
+      <c r="F146">
+        <v>0</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>40</v>
+      </c>
+      <c r="B147" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147" t="s">
+        <v>24</v>
+      </c>
+      <c r="D147">
+        <v>137</v>
+      </c>
+      <c r="E147">
+        <v>604515</v>
+      </c>
+      <c r="F147">
+        <v>652</v>
+      </c>
+      <c r="G147">
+        <v>91530</v>
+      </c>
+      <c r="H147">
+        <v>99</v>
+      </c>
+      <c r="I147">
+        <v>696045</v>
+      </c>
+      <c r="J147">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>40</v>
+      </c>
+      <c r="B148" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148" t="s">
+        <v>25</v>
+      </c>
+      <c r="D148">
+        <v>137</v>
+      </c>
+      <c r="E148">
+        <v>542051</v>
+      </c>
+      <c r="F148">
+        <v>585</v>
+      </c>
+      <c r="G148">
+        <v>71547</v>
+      </c>
+      <c r="H148">
+        <v>77</v>
+      </c>
+      <c r="I148">
+        <v>613598</v>
+      </c>
+      <c r="J148">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>40</v>
+      </c>
+      <c r="B149" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" t="s">
+        <v>26</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="E149">
+        <v>0</v>
+      </c>
+      <c r="F149">
+        <v>0</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>40</v>
+      </c>
+      <c r="B150" t="s">
+        <v>27</v>
+      </c>
+      <c r="C150" t="s">
+        <v>28</v>
+      </c>
+      <c r="D150" s="1">
+        <v>7761</v>
+      </c>
+      <c r="E150">
+        <v>75761</v>
+      </c>
+      <c r="F150">
+        <v>20476</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+      <c r="I150">
+        <v>75761</v>
+      </c>
+      <c r="J150">
+        <v>20476</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>40</v>
+      </c>
+      <c r="B151" t="s">
+        <v>29</v>
+      </c>
+      <c r="C151" t="s">
+        <v>30</v>
+      </c>
+      <c r="D151" s="1">
+        <v>4721</v>
+      </c>
+      <c r="E151">
+        <v>16516</v>
+      </c>
+      <c r="F151">
+        <v>16516</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+      <c r="I151">
+        <v>16516</v>
+      </c>
+      <c r="J151">
+        <v>16516</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>40</v>
+      </c>
+      <c r="B152" t="s">
+        <v>27</v>
+      </c>
+      <c r="C152" t="s">
+        <v>31</v>
+      </c>
+      <c r="D152">
+        <v>158</v>
+      </c>
+      <c r="E152">
+        <v>2103</v>
+      </c>
+      <c r="F152">
+        <v>568</v>
+      </c>
+      <c r="G152">
+        <v>421</v>
+      </c>
+      <c r="H152">
+        <v>114</v>
+      </c>
+      <c r="I152">
+        <v>2524</v>
+      </c>
+      <c r="J152">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>40</v>
+      </c>
+      <c r="B153" t="s">
+        <v>27</v>
+      </c>
+      <c r="C153" t="s">
+        <v>32</v>
+      </c>
+      <c r="D153">
+        <v>742</v>
+      </c>
+      <c r="E153">
+        <v>7228</v>
+      </c>
+      <c r="F153">
+        <v>1953</v>
+      </c>
+      <c r="G153">
+        <v>1150</v>
+      </c>
+      <c r="H153">
+        <v>311</v>
+      </c>
+      <c r="I153">
+        <v>8378</v>
+      </c>
+      <c r="J153">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>39</v>
+      </c>
+      <c r="B154" t="s">
+        <v>11</v>
+      </c>
+      <c r="C154" t="s">
+        <v>12</v>
+      </c>
+      <c r="D154" s="1">
+        <v>22450</v>
+      </c>
+      <c r="E154">
+        <v>96792060</v>
+      </c>
+      <c r="F154">
+        <v>104640</v>
+      </c>
+      <c r="G154">
+        <v>9090714</v>
+      </c>
+      <c r="H154">
+        <v>9828</v>
+      </c>
+      <c r="I154">
+        <v>105882774</v>
+      </c>
+      <c r="J154">
+        <v>114468</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>39</v>
+      </c>
+      <c r="B155" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" t="s">
+        <v>13</v>
+      </c>
+      <c r="D155" s="1">
+        <v>25213</v>
+      </c>
+      <c r="E155">
+        <v>98574613</v>
+      </c>
+      <c r="F155">
+        <v>106567</v>
+      </c>
+      <c r="G155">
+        <v>16844866</v>
+      </c>
+      <c r="H155">
+        <v>18211</v>
+      </c>
+      <c r="I155">
+        <v>115419479</v>
+      </c>
+      <c r="J155">
+        <v>124778</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>39</v>
+      </c>
+      <c r="B156" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" t="s">
+        <v>14</v>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+      <c r="E156">
+        <v>0</v>
+      </c>
+      <c r="F156">
+        <v>0</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>39</v>
+      </c>
+      <c r="B157" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" t="s">
+        <v>15</v>
+      </c>
+      <c r="D157" s="1">
+        <v>3510</v>
+      </c>
+      <c r="E157">
+        <v>10554430</v>
+      </c>
+      <c r="F157">
+        <v>11410</v>
+      </c>
+      <c r="G157">
+        <v>1006036</v>
+      </c>
+      <c r="H157">
+        <v>1088</v>
+      </c>
+      <c r="I157">
+        <v>11560466</v>
+      </c>
+      <c r="J157">
+        <v>12498</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>39</v>
+      </c>
+      <c r="B158" t="s">
+        <v>11</v>
+      </c>
+      <c r="C158" t="s">
+        <v>16</v>
+      </c>
+      <c r="D158" s="1">
+        <v>1381</v>
+      </c>
+      <c r="E158">
+        <v>3511690</v>
+      </c>
+      <c r="F158">
+        <v>3797</v>
+      </c>
+      <c r="G158">
+        <v>256369</v>
+      </c>
+      <c r="H158">
+        <v>277</v>
+      </c>
+      <c r="I158">
+        <v>3768059</v>
+      </c>
+      <c r="J158">
+        <v>4074</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>39</v>
+      </c>
+      <c r="B159" t="s">
+        <v>11</v>
+      </c>
+      <c r="C159" t="s">
+        <v>17</v>
+      </c>
+      <c r="D159" s="1">
+        <v>1160</v>
+      </c>
+      <c r="E159">
+        <v>2931970</v>
+      </c>
+      <c r="F159">
+        <v>3170</v>
+      </c>
+      <c r="G159">
+        <v>375074</v>
+      </c>
+      <c r="H159">
+        <v>405</v>
+      </c>
+      <c r="I159">
+        <v>3307044</v>
+      </c>
+      <c r="J159">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>39</v>
+      </c>
+      <c r="B160" t="s">
+        <v>11</v>
+      </c>
+      <c r="C160" t="s">
+        <v>18</v>
+      </c>
+      <c r="D160">
+        <v>956</v>
+      </c>
+      <c r="E160">
+        <v>3650467</v>
+      </c>
+      <c r="F160">
+        <v>3947</v>
+      </c>
+      <c r="G160">
+        <v>638637</v>
+      </c>
+      <c r="H160">
+        <v>690</v>
+      </c>
+      <c r="I160">
+        <v>4289104</v>
+      </c>
+      <c r="J160">
+        <v>4637</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>39</v>
+      </c>
+      <c r="B161" t="s">
+        <v>11</v>
+      </c>
+      <c r="C161" t="s">
+        <v>19</v>
+      </c>
+      <c r="D161">
+        <v>567</v>
+      </c>
+      <c r="E161">
+        <v>1837387</v>
+      </c>
+      <c r="F161">
+        <v>1987</v>
+      </c>
+      <c r="G161">
+        <v>279916</v>
+      </c>
+      <c r="H161">
+        <v>302</v>
+      </c>
+      <c r="I161">
+        <v>2117303</v>
+      </c>
+      <c r="J161">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>39</v>
+      </c>
+      <c r="B162" t="s">
+        <v>11</v>
+      </c>
+      <c r="C162" t="s">
+        <v>20</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="E162">
+        <v>0</v>
+      </c>
+      <c r="F162">
+        <v>0</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>39</v>
+      </c>
+      <c r="B163" t="s">
+        <v>11</v>
+      </c>
+      <c r="C163" t="s">
+        <v>21</v>
+      </c>
+      <c r="D163">
+        <v>407</v>
+      </c>
+      <c r="E163">
+        <v>1286519</v>
+      </c>
+      <c r="F163">
+        <v>1391</v>
+      </c>
+      <c r="G163">
+        <v>213382</v>
+      </c>
+      <c r="H163">
+        <v>231</v>
+      </c>
+      <c r="I163">
+        <v>1499901</v>
+      </c>
+      <c r="J163">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>39</v>
+      </c>
+      <c r="B164" t="s">
+        <v>11</v>
+      </c>
+      <c r="C164" t="s">
+        <v>22</v>
+      </c>
+      <c r="D164">
+        <v>638</v>
+      </c>
+      <c r="E164">
+        <v>2846424</v>
+      </c>
+      <c r="F164">
+        <v>3077</v>
+      </c>
+      <c r="G164">
+        <v>406725</v>
+      </c>
+      <c r="H164">
+        <v>440</v>
+      </c>
+      <c r="I164">
+        <v>3253149</v>
+      </c>
+      <c r="J164">
+        <v>3517</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>39</v>
+      </c>
+      <c r="B165" t="s">
+        <v>11</v>
+      </c>
+      <c r="C165" t="s">
+        <v>23</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="E165">
+        <v>0</v>
+      </c>
+      <c r="F165">
+        <v>0</v>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>39</v>
+      </c>
+      <c r="B166" t="s">
+        <v>11</v>
+      </c>
+      <c r="C166" t="s">
+        <v>24</v>
+      </c>
+      <c r="D166">
+        <v>150</v>
+      </c>
+      <c r="E166">
+        <v>661878</v>
+      </c>
+      <c r="F166">
+        <v>716</v>
+      </c>
+      <c r="G166">
+        <v>100215</v>
+      </c>
+      <c r="H166">
+        <v>108</v>
+      </c>
+      <c r="I166">
+        <v>762093</v>
+      </c>
+      <c r="J166">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>39</v>
+      </c>
+      <c r="B167" t="s">
+        <v>11</v>
+      </c>
+      <c r="C167" t="s">
+        <v>25</v>
+      </c>
+      <c r="D167">
+        <v>138</v>
+      </c>
+      <c r="E167">
+        <v>546008</v>
+      </c>
+      <c r="F167">
+        <v>590</v>
+      </c>
+      <c r="G167">
+        <v>72069</v>
+      </c>
+      <c r="H167">
+        <v>78</v>
+      </c>
+      <c r="I167">
+        <v>618077</v>
+      </c>
+      <c r="J167">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>39</v>
+      </c>
+      <c r="B168" t="s">
+        <v>11</v>
+      </c>
+      <c r="C168" t="s">
+        <v>26</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="E168">
+        <v>0</v>
+      </c>
+      <c r="F168">
+        <v>0</v>
+      </c>
+      <c r="G168">
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>39</v>
+      </c>
+      <c r="B169" t="s">
+        <v>27</v>
+      </c>
+      <c r="C169" t="s">
+        <v>28</v>
+      </c>
+      <c r="D169" s="1">
+        <v>9854</v>
+      </c>
+      <c r="E169">
+        <v>96191</v>
+      </c>
+      <c r="F169">
+        <v>25998</v>
+      </c>
+      <c r="G169">
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>96191</v>
+      </c>
+      <c r="J169">
+        <v>25998</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>39</v>
+      </c>
+      <c r="B170" t="s">
+        <v>29</v>
+      </c>
+      <c r="C170" t="s">
+        <v>30</v>
+      </c>
+      <c r="D170" s="1">
+        <v>4616</v>
+      </c>
+      <c r="E170">
+        <v>16150</v>
+      </c>
+      <c r="F170">
+        <v>16150</v>
+      </c>
+      <c r="G170">
+        <v>0</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170">
+        <v>16150</v>
+      </c>
+      <c r="J170">
+        <v>16150</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>39</v>
+      </c>
+      <c r="B171" t="s">
+        <v>27</v>
+      </c>
+      <c r="C171" t="s">
+        <v>31</v>
+      </c>
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="E171">
+        <v>0</v>
+      </c>
+      <c r="F171">
+        <v>0</v>
+      </c>
+      <c r="G171">
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>39</v>
+      </c>
+      <c r="B172" t="s">
+        <v>27</v>
+      </c>
+      <c r="C172" t="s">
+        <v>32</v>
+      </c>
+      <c r="D172">
+        <v>366</v>
+      </c>
+      <c r="E172">
+        <v>3566</v>
+      </c>
+      <c r="F172">
+        <v>964</v>
+      </c>
+      <c r="G172">
+        <v>567</v>
+      </c>
+      <c r="H172">
+        <v>153</v>
+      </c>
+      <c r="I172">
+        <v>4133</v>
+      </c>
+      <c r="J172">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>38</v>
+      </c>
+      <c r="B173" t="s">
+        <v>11</v>
+      </c>
+      <c r="C173" t="s">
+        <v>12</v>
+      </c>
+      <c r="D173" s="1">
+        <v>44459</v>
+      </c>
+      <c r="E173">
+        <v>191686236</v>
+      </c>
+      <c r="F173">
+        <v>207229</v>
+      </c>
+      <c r="G173">
+        <v>18003179</v>
+      </c>
+      <c r="H173">
+        <v>19462</v>
+      </c>
+      <c r="I173">
+        <v>209689415</v>
+      </c>
+      <c r="J173">
+        <v>226691</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>38</v>
+      </c>
+      <c r="B174" t="s">
+        <v>11</v>
+      </c>
+      <c r="C174" t="s">
+        <v>13</v>
+      </c>
+      <c r="D174" s="1">
+        <v>44040</v>
+      </c>
+      <c r="E174">
+        <v>172181154</v>
+      </c>
+      <c r="F174">
+        <v>186142</v>
+      </c>
+      <c r="G174">
+        <v>29423078</v>
+      </c>
+      <c r="H174">
+        <v>31809</v>
+      </c>
+      <c r="I174">
+        <v>201604232</v>
+      </c>
+      <c r="J174">
+        <v>217951</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>38</v>
+      </c>
+      <c r="B175" t="s">
+        <v>11</v>
+      </c>
+      <c r="C175" t="s">
+        <v>14</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
+      <c r="F175">
+        <v>0</v>
+      </c>
+      <c r="G175">
+        <v>0</v>
+      </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>38</v>
+      </c>
+      <c r="B176" t="s">
+        <v>11</v>
+      </c>
+      <c r="C176" t="s">
+        <v>15</v>
+      </c>
+      <c r="D176" s="1">
+        <v>4955</v>
+      </c>
+      <c r="E176">
+        <v>14899487</v>
+      </c>
+      <c r="F176">
+        <v>16108</v>
+      </c>
+      <c r="G176">
+        <v>1420202</v>
+      </c>
+      <c r="H176">
+        <v>1535</v>
+      </c>
+      <c r="I176">
+        <v>16319689</v>
+      </c>
+      <c r="J176">
+        <v>17643</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>38</v>
+      </c>
+      <c r="B177" t="s">
+        <v>11</v>
+      </c>
+      <c r="C177" t="s">
+        <v>16</v>
+      </c>
+      <c r="D177" s="1">
+        <v>2083</v>
+      </c>
+      <c r="E177">
+        <v>5296778</v>
+      </c>
+      <c r="F177">
+        <v>5726</v>
+      </c>
+      <c r="G177">
+        <v>386688</v>
+      </c>
+      <c r="H177">
+        <v>418</v>
+      </c>
+      <c r="I177">
+        <v>5683466</v>
+      </c>
+      <c r="J177">
+        <v>6144</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>38</v>
+      </c>
+      <c r="B178" t="s">
+        <v>11</v>
+      </c>
+      <c r="C178" t="s">
+        <v>17</v>
+      </c>
+      <c r="D178" s="1">
+        <v>1820</v>
+      </c>
+      <c r="E178">
+        <v>4600159</v>
+      </c>
+      <c r="F178">
+        <v>4973</v>
+      </c>
+      <c r="G178">
+        <v>588479</v>
+      </c>
+      <c r="H178">
+        <v>636</v>
+      </c>
+      <c r="I178">
+        <v>5188638</v>
+      </c>
+      <c r="J178">
+        <v>5609</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>38</v>
+      </c>
+      <c r="B179" t="s">
+        <v>11</v>
+      </c>
+      <c r="C179" t="s">
+        <v>18</v>
+      </c>
+      <c r="D179">
+        <v>783</v>
+      </c>
+      <c r="E179">
+        <v>2990947</v>
+      </c>
+      <c r="F179">
+        <v>3233</v>
+      </c>
+      <c r="G179">
+        <v>523256</v>
+      </c>
+      <c r="H179">
+        <v>566</v>
+      </c>
+      <c r="I179">
+        <v>3514203</v>
+      </c>
+      <c r="J179">
+        <v>3799</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>38</v>
+      </c>
+      <c r="B180" t="s">
+        <v>11</v>
+      </c>
+      <c r="C180" t="s">
+        <v>19</v>
+      </c>
+      <c r="D180">
+        <v>662</v>
+      </c>
+      <c r="E180">
+        <v>2145238</v>
+      </c>
+      <c r="F180">
+        <v>2319</v>
+      </c>
+      <c r="G180">
+        <v>326816</v>
+      </c>
+      <c r="H180">
+        <v>353</v>
+      </c>
+      <c r="I180">
+        <v>2472054</v>
+      </c>
+      <c r="J180">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>38</v>
+      </c>
+      <c r="B181" t="s">
+        <v>11</v>
+      </c>
+      <c r="C181" t="s">
+        <v>20</v>
+      </c>
+      <c r="D181">
+        <v>0</v>
+      </c>
+      <c r="E181">
+        <v>0</v>
+      </c>
+      <c r="F181">
+        <v>0</v>
+      </c>
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>38</v>
+      </c>
+      <c r="B182" t="s">
+        <v>11</v>
+      </c>
+      <c r="C182" t="s">
+        <v>21</v>
+      </c>
+      <c r="D182">
+        <v>320</v>
+      </c>
+      <c r="E182">
+        <v>1011513</v>
+      </c>
+      <c r="F182">
+        <v>1094</v>
+      </c>
+      <c r="G182">
+        <v>167770</v>
+      </c>
+      <c r="H182">
+        <v>181</v>
+      </c>
+      <c r="I182">
+        <v>1179283</v>
+      </c>
+      <c r="J182">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>38</v>
+      </c>
+      <c r="B183" t="s">
+        <v>11</v>
+      </c>
+      <c r="C183" t="s">
+        <v>22</v>
+      </c>
+      <c r="D183">
+        <v>636</v>
+      </c>
+      <c r="E183">
+        <v>2837501</v>
+      </c>
+      <c r="F183">
+        <v>3068</v>
+      </c>
+      <c r="G183">
+        <v>405450</v>
+      </c>
+      <c r="H183">
+        <v>438</v>
+      </c>
+      <c r="I183">
+        <v>3242951</v>
+      </c>
+      <c r="J183">
+        <v>3506</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>38</v>
+      </c>
+      <c r="B184" t="s">
+        <v>11</v>
+      </c>
+      <c r="C184" t="s">
+        <v>23</v>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="E184">
+        <v>0</v>
+      </c>
+      <c r="F184">
+        <v>0</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>38</v>
+      </c>
+      <c r="B185" t="s">
+        <v>11</v>
+      </c>
+      <c r="C185" t="s">
+        <v>24</v>
+      </c>
+      <c r="D185">
+        <v>162</v>
+      </c>
+      <c r="E185">
+        <v>714828</v>
+      </c>
+      <c r="F185">
+        <v>773</v>
+      </c>
+      <c r="G185">
+        <v>108232</v>
+      </c>
+      <c r="H185">
+        <v>117</v>
+      </c>
+      <c r="I185">
+        <v>823060</v>
+      </c>
+      <c r="J185">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>38</v>
+      </c>
+      <c r="B186" t="s">
+        <v>11</v>
+      </c>
+      <c r="C186" t="s">
+        <v>25</v>
+      </c>
+      <c r="D186">
+        <v>200</v>
+      </c>
+      <c r="E186">
+        <v>791316</v>
+      </c>
+      <c r="F186">
+        <v>855</v>
+      </c>
+      <c r="G186">
+        <v>104448</v>
+      </c>
+      <c r="H186">
+        <v>113</v>
+      </c>
+      <c r="I186">
+        <v>895764</v>
+      </c>
+      <c r="J186">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>38</v>
+      </c>
+      <c r="B187" t="s">
+        <v>11</v>
+      </c>
+      <c r="C187" t="s">
+        <v>26</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="E187">
+        <v>0</v>
+      </c>
+      <c r="F187">
+        <v>0</v>
+      </c>
+      <c r="G187">
+        <v>0</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>38</v>
+      </c>
+      <c r="B188" t="s">
+        <v>27</v>
+      </c>
+      <c r="C188" t="s">
+        <v>28</v>
+      </c>
+      <c r="D188" s="1">
+        <v>9387</v>
+      </c>
+      <c r="E188">
+        <v>91631</v>
+      </c>
+      <c r="F188">
+        <v>24765</v>
+      </c>
+      <c r="G188">
+        <v>0</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+      <c r="I188">
+        <v>91631</v>
+      </c>
+      <c r="J188">
+        <v>24765</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>38</v>
+      </c>
+      <c r="B189" t="s">
+        <v>29</v>
+      </c>
+      <c r="C189" t="s">
+        <v>30</v>
+      </c>
+      <c r="D189" s="1">
+        <v>5240</v>
+      </c>
+      <c r="E189">
+        <v>18332</v>
+      </c>
+      <c r="F189">
+        <v>18332</v>
+      </c>
+      <c r="G189">
+        <v>0</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
+      </c>
+      <c r="I189">
+        <v>18332</v>
+      </c>
+      <c r="J189">
+        <v>18332</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>38</v>
+      </c>
+      <c r="B190" t="s">
+        <v>27</v>
+      </c>
+      <c r="C190" t="s">
+        <v>31</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="E190">
+        <v>0</v>
+      </c>
+      <c r="F190">
+        <v>0</v>
+      </c>
+      <c r="G190">
+        <v>0</v>
+      </c>
+      <c r="H190">
+        <v>0</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>38</v>
+      </c>
+      <c r="B191" t="s">
+        <v>27</v>
+      </c>
+      <c r="C191" t="s">
+        <v>32</v>
+      </c>
+      <c r="D191">
+        <v>353</v>
+      </c>
+      <c r="E191">
+        <v>3439</v>
+      </c>
+      <c r="F191">
+        <v>929</v>
+      </c>
+      <c r="G191">
+        <v>547</v>
+      </c>
+      <c r="H191">
+        <v>148</v>
+      </c>
+      <c r="I191">
+        <v>3986</v>
+      </c>
+      <c r="J191">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>37</v>
+      </c>
+      <c r="B192" t="s">
+        <v>11</v>
+      </c>
+      <c r="C192" t="s">
+        <v>12</v>
+      </c>
+      <c r="D192" s="1">
+        <v>32574</v>
+      </c>
+      <c r="E192">
+        <v>140443381</v>
+      </c>
+      <c r="F192">
+        <v>151831</v>
+      </c>
+      <c r="G192">
+        <v>13190448</v>
+      </c>
+      <c r="H192">
+        <v>14260</v>
+      </c>
+      <c r="I192">
+        <v>153633829</v>
+      </c>
+      <c r="J192">
+        <v>166091</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>37</v>
+      </c>
+      <c r="B193" t="s">
+        <v>11</v>
+      </c>
+      <c r="C193" t="s">
+        <v>13</v>
+      </c>
+      <c r="D193" s="1">
+        <v>40474</v>
+      </c>
+      <c r="E193">
+        <v>158240520</v>
+      </c>
+      <c r="F193">
+        <v>171071</v>
+      </c>
+      <c r="G193">
+        <v>27040841</v>
+      </c>
+      <c r="H193">
+        <v>29233</v>
+      </c>
+      <c r="I193">
+        <v>185281361</v>
+      </c>
+      <c r="J193">
+        <v>200304</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>37</v>
+      </c>
+      <c r="B194" t="s">
+        <v>11</v>
+      </c>
+      <c r="C194" t="s">
+        <v>14</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="E194">
+        <v>0</v>
+      </c>
+      <c r="F194">
+        <v>0</v>
+      </c>
+      <c r="G194">
+        <v>0</v>
+      </c>
+      <c r="H194">
+        <v>0</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>37</v>
+      </c>
+      <c r="B195" t="s">
+        <v>11</v>
+      </c>
+      <c r="C195" t="s">
+        <v>15</v>
+      </c>
+      <c r="D195" s="1">
+        <v>3651</v>
+      </c>
+      <c r="E195">
+        <v>10978411</v>
+      </c>
+      <c r="F195">
+        <v>11869</v>
+      </c>
+      <c r="G195">
+        <v>1046450</v>
+      </c>
+      <c r="H195">
+        <v>1131</v>
+      </c>
+      <c r="I195">
+        <v>12024861</v>
+      </c>
+      <c r="J195">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>37</v>
+      </c>
+      <c r="B196" t="s">
+        <v>11</v>
+      </c>
+      <c r="C196" t="s">
+        <v>16</v>
+      </c>
+      <c r="D196" s="1">
+        <v>1782</v>
+      </c>
+      <c r="E196">
+        <v>4531377</v>
+      </c>
+      <c r="F196">
+        <v>4898</v>
+      </c>
+      <c r="G196">
+        <v>330810</v>
+      </c>
+      <c r="H196">
+        <v>358</v>
+      </c>
+      <c r="I196">
+        <v>4862187</v>
+      </c>
+      <c r="J196">
+        <v>5256</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>37</v>
+      </c>
+      <c r="B197" t="s">
+        <v>11</v>
+      </c>
+      <c r="C197" t="s">
+        <v>17</v>
+      </c>
+      <c r="D197" s="1">
+        <v>1128</v>
+      </c>
+      <c r="E197">
+        <v>2851087</v>
+      </c>
+      <c r="F197">
+        <v>3083</v>
+      </c>
+      <c r="G197">
+        <v>364728</v>
+      </c>
+      <c r="H197">
+        <v>394</v>
+      </c>
+      <c r="I197">
+        <v>3215815</v>
+      </c>
+      <c r="J197">
+        <v>3477</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>37</v>
+      </c>
+      <c r="B198" t="s">
+        <v>11</v>
+      </c>
+      <c r="C198" t="s">
+        <v>18</v>
+      </c>
+      <c r="D198" s="1">
+        <v>1037</v>
+      </c>
+      <c r="E198">
+        <v>3961324</v>
+      </c>
+      <c r="F198">
+        <v>4283</v>
+      </c>
+      <c r="G198">
+        <v>693020</v>
+      </c>
+      <c r="H198">
+        <v>749</v>
+      </c>
+      <c r="I198">
+        <v>4654344</v>
+      </c>
+      <c r="J198">
+        <v>5032</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>37</v>
+      </c>
+      <c r="B199" t="s">
+        <v>11</v>
+      </c>
+      <c r="C199" t="s">
+        <v>19</v>
+      </c>
+      <c r="D199" s="1">
+        <v>1303</v>
+      </c>
+      <c r="E199">
+        <v>4222424</v>
+      </c>
+      <c r="F199">
+        <v>4564</v>
+      </c>
+      <c r="G199">
+        <v>643265</v>
+      </c>
+      <c r="H199">
+        <v>696</v>
+      </c>
+      <c r="I199">
+        <v>4865689</v>
+      </c>
+      <c r="J199">
+        <v>5260</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>37</v>
+      </c>
+      <c r="B200" t="s">
+        <v>11</v>
+      </c>
+      <c r="C200" t="s">
+        <v>20</v>
+      </c>
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="E200">
+        <v>0</v>
+      </c>
+      <c r="F200">
+        <v>0</v>
+      </c>
+      <c r="G200">
+        <v>0</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>37</v>
+      </c>
+      <c r="B201" t="s">
+        <v>11</v>
+      </c>
+      <c r="C201" t="s">
+        <v>21</v>
+      </c>
+      <c r="D201">
+        <v>476</v>
+      </c>
+      <c r="E201">
+        <v>1504627</v>
+      </c>
+      <c r="F201">
+        <v>1626</v>
+      </c>
+      <c r="G201">
+        <v>249557</v>
+      </c>
+      <c r="H201">
+        <v>270</v>
+      </c>
+      <c r="I201">
+        <v>1754184</v>
+      </c>
+      <c r="J201">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>37</v>
+      </c>
+      <c r="B202" t="s">
+        <v>11</v>
+      </c>
+      <c r="C202" t="s">
+        <v>22</v>
+      </c>
+      <c r="D202">
+        <v>496</v>
+      </c>
+      <c r="E202">
+        <v>2212894</v>
+      </c>
+      <c r="F202">
+        <v>2392</v>
+      </c>
+      <c r="G202">
+        <v>316200</v>
+      </c>
+      <c r="H202">
+        <v>342</v>
+      </c>
+      <c r="I202">
+        <v>2529094</v>
+      </c>
+      <c r="J202">
+        <v>2734</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>37</v>
+      </c>
+      <c r="B203" t="s">
+        <v>11</v>
+      </c>
+      <c r="C203" t="s">
+        <v>23</v>
+      </c>
+      <c r="D203">
+        <v>0</v>
+      </c>
+      <c r="E203">
+        <v>0</v>
+      </c>
+      <c r="F203">
+        <v>0</v>
+      </c>
+      <c r="G203">
+        <v>0</v>
+      </c>
+      <c r="H203">
+        <v>0</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>37</v>
+      </c>
+      <c r="B204" t="s">
+        <v>11</v>
+      </c>
+      <c r="C204" t="s">
+        <v>24</v>
+      </c>
+      <c r="D204">
+        <v>150</v>
+      </c>
+      <c r="E204">
+        <v>661878</v>
+      </c>
+      <c r="F204">
+        <v>716</v>
+      </c>
+      <c r="G204">
+        <v>100215</v>
+      </c>
+      <c r="H204">
+        <v>108</v>
+      </c>
+      <c r="I204">
+        <v>762093</v>
+      </c>
+      <c r="J204">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>37</v>
+      </c>
+      <c r="B205" t="s">
+        <v>11</v>
+      </c>
+      <c r="C205" t="s">
+        <v>25</v>
+      </c>
+      <c r="D205">
+        <v>160</v>
+      </c>
+      <c r="E205">
+        <v>633053</v>
+      </c>
+      <c r="F205">
+        <v>685</v>
+      </c>
+      <c r="G205">
+        <v>83558</v>
+      </c>
+      <c r="H205">
+        <v>90</v>
+      </c>
+      <c r="I205">
+        <v>716611</v>
+      </c>
+      <c r="J205">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>37</v>
+      </c>
+      <c r="B206" t="s">
+        <v>11</v>
+      </c>
+      <c r="C206" t="s">
+        <v>26</v>
+      </c>
+      <c r="D206">
+        <v>0</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+      <c r="F206">
+        <v>0</v>
+      </c>
+      <c r="G206">
+        <v>0</v>
+      </c>
+      <c r="H206">
+        <v>0</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>37</v>
+      </c>
+      <c r="B207" t="s">
+        <v>27</v>
+      </c>
+      <c r="C207" t="s">
+        <v>28</v>
+      </c>
+      <c r="D207" s="1">
+        <v>14743</v>
+      </c>
+      <c r="E207">
+        <v>143912</v>
+      </c>
+      <c r="F207">
+        <v>38895</v>
+      </c>
+      <c r="G207">
+        <v>0</v>
+      </c>
+      <c r="H207">
+        <v>0</v>
+      </c>
+      <c r="I207">
+        <v>143912</v>
+      </c>
+      <c r="J207">
+        <v>38895</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>37</v>
+      </c>
+      <c r="B208" t="s">
+        <v>29</v>
+      </c>
+      <c r="C208" t="s">
+        <v>30</v>
+      </c>
+      <c r="D208" s="1">
+        <v>6851</v>
+      </c>
+      <c r="E208">
+        <v>23970</v>
+      </c>
+      <c r="F208">
+        <v>23970</v>
+      </c>
+      <c r="G208">
+        <v>0</v>
+      </c>
+      <c r="H208">
+        <v>0</v>
+      </c>
+      <c r="I208">
+        <v>23970</v>
+      </c>
+      <c r="J208">
+        <v>23970</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>37</v>
+      </c>
+      <c r="B209" t="s">
+        <v>27</v>
+      </c>
+      <c r="C209" t="s">
+        <v>31</v>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
+      <c r="F209">
+        <v>0</v>
+      </c>
+      <c r="G209">
+        <v>0</v>
+      </c>
+      <c r="H209">
+        <v>0</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>37</v>
+      </c>
+      <c r="B210" t="s">
+        <v>27</v>
+      </c>
+      <c r="C210" t="s">
+        <v>32</v>
+      </c>
+      <c r="D210">
+        <v>457</v>
+      </c>
+      <c r="E210">
+        <v>4451</v>
+      </c>
+      <c r="F210">
+        <v>1204</v>
+      </c>
+      <c r="G210">
+        <v>709</v>
+      </c>
+      <c r="H210">
+        <v>191</v>
+      </c>
+      <c r="I210">
+        <v>5160</v>
+      </c>
+      <c r="J210">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>36</v>
+      </c>
+      <c r="B211" t="s">
+        <v>11</v>
+      </c>
+      <c r="C211" t="s">
+        <v>12</v>
+      </c>
+      <c r="D211" s="1">
+        <v>44899</v>
+      </c>
+      <c r="E211">
+        <v>193584121</v>
+      </c>
+      <c r="F211">
+        <v>209281</v>
+      </c>
+      <c r="G211">
+        <v>18181427</v>
+      </c>
+      <c r="H211">
+        <v>19655</v>
+      </c>
+      <c r="I211">
+        <v>211765548</v>
+      </c>
+      <c r="J211">
+        <v>228936</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>36</v>
+      </c>
+      <c r="B212" t="s">
+        <v>11</v>
+      </c>
+      <c r="C212" t="s">
+        <v>13</v>
+      </c>
+      <c r="D212" s="1">
+        <v>32032</v>
+      </c>
+      <c r="E212">
+        <v>125234229</v>
+      </c>
+      <c r="F212">
+        <v>135388</v>
+      </c>
+      <c r="G212">
+        <v>21400579</v>
+      </c>
+      <c r="H212">
+        <v>23136</v>
+      </c>
+      <c r="I212">
+        <v>146634808</v>
+      </c>
+      <c r="J212">
+        <v>158524</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>36</v>
+      </c>
+      <c r="B213" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213" t="s">
+        <v>14</v>
+      </c>
+      <c r="D213">
+        <v>0</v>
+      </c>
+      <c r="E213">
+        <v>0</v>
+      </c>
+      <c r="F213">
+        <v>0</v>
+      </c>
+      <c r="G213">
+        <v>0</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>36</v>
+      </c>
+      <c r="B214" t="s">
+        <v>11</v>
+      </c>
+      <c r="C214" t="s">
+        <v>15</v>
+      </c>
+      <c r="D214" s="1">
+        <v>4463</v>
+      </c>
+      <c r="E214">
+        <v>13420063</v>
+      </c>
+      <c r="F214">
+        <v>14508</v>
+      </c>
+      <c r="G214">
+        <v>1279185</v>
+      </c>
+      <c r="H214">
+        <v>1383</v>
+      </c>
+      <c r="I214">
+        <v>14699248</v>
+      </c>
+      <c r="J214">
+        <v>15891</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>36</v>
+      </c>
+      <c r="B215" t="s">
+        <v>11</v>
+      </c>
+      <c r="C215" t="s">
+        <v>16</v>
+      </c>
+      <c r="D215" s="1">
+        <v>2407</v>
+      </c>
+      <c r="E215">
+        <v>6120665</v>
+      </c>
+      <c r="F215">
+        <v>6617</v>
+      </c>
+      <c r="G215">
+        <v>446835</v>
+      </c>
+      <c r="H215">
+        <v>483</v>
+      </c>
+      <c r="I215">
+        <v>6567500</v>
+      </c>
+      <c r="J215">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>36</v>
+      </c>
+      <c r="B216" t="s">
+        <v>11</v>
+      </c>
+      <c r="C216" t="s">
+        <v>17</v>
+      </c>
+      <c r="D216" s="1">
+        <v>1480</v>
+      </c>
+      <c r="E216">
+        <v>3740789</v>
+      </c>
+      <c r="F216">
+        <v>4044</v>
+      </c>
+      <c r="G216">
+        <v>478543</v>
+      </c>
+      <c r="H216">
+        <v>517</v>
+      </c>
+      <c r="I216">
+        <v>4219332</v>
+      </c>
+      <c r="J216">
+        <v>4561</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>36</v>
+      </c>
+      <c r="B217" t="s">
+        <v>11</v>
+      </c>
+      <c r="C217" t="s">
+        <v>18</v>
+      </c>
+      <c r="D217">
+        <v>956</v>
+      </c>
+      <c r="E217">
+        <v>3650467</v>
+      </c>
+      <c r="F217">
+        <v>3947</v>
+      </c>
+      <c r="G217">
+        <v>638637</v>
+      </c>
+      <c r="H217">
+        <v>690</v>
+      </c>
+      <c r="I217">
+        <v>4289104</v>
+      </c>
+      <c r="J217">
+        <v>4637</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>36</v>
+      </c>
+      <c r="B218" t="s">
+        <v>11</v>
+      </c>
+      <c r="C218" t="s">
+        <v>19</v>
+      </c>
+      <c r="D218">
+        <v>837</v>
+      </c>
+      <c r="E218">
+        <v>2712332</v>
+      </c>
+      <c r="F218">
+        <v>2932</v>
+      </c>
+      <c r="G218">
+        <v>413210</v>
+      </c>
+      <c r="H218">
+        <v>447</v>
+      </c>
+      <c r="I218">
+        <v>3125542</v>
+      </c>
+      <c r="J218">
+        <v>3379</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>36</v>
+      </c>
+      <c r="B219" t="s">
+        <v>11</v>
+      </c>
+      <c r="C219" t="s">
+        <v>20</v>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+      <c r="E219">
+        <v>0</v>
+      </c>
+      <c r="F219">
+        <v>0</v>
+      </c>
+      <c r="G219">
+        <v>0</v>
+      </c>
+      <c r="H219">
+        <v>0</v>
+      </c>
+      <c r="I219">
+        <v>0</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>36</v>
+      </c>
+      <c r="B220" t="s">
+        <v>11</v>
+      </c>
+      <c r="C220" t="s">
+        <v>21</v>
+      </c>
+      <c r="D220">
+        <v>887</v>
+      </c>
+      <c r="E220">
+        <v>2803790</v>
+      </c>
+      <c r="F220">
+        <v>3031</v>
+      </c>
+      <c r="G220">
+        <v>465036</v>
+      </c>
+      <c r="H220">
+        <v>503</v>
+      </c>
+      <c r="I220">
+        <v>3268826</v>
+      </c>
+      <c r="J220">
+        <v>3534</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>36</v>
+      </c>
+      <c r="B221" t="s">
+        <v>11</v>
+      </c>
+      <c r="C221" t="s">
+        <v>22</v>
+      </c>
+      <c r="D221">
+        <v>262</v>
+      </c>
+      <c r="E221">
+        <v>1168908</v>
+      </c>
+      <c r="F221">
+        <v>1263</v>
+      </c>
+      <c r="G221">
+        <v>167025</v>
+      </c>
+      <c r="H221">
+        <v>181</v>
+      </c>
+      <c r="I221">
+        <v>1335933</v>
+      </c>
+      <c r="J221">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>36</v>
+      </c>
+      <c r="B222" t="s">
+        <v>11</v>
+      </c>
+      <c r="C222" t="s">
+        <v>23</v>
+      </c>
+      <c r="D222">
+        <v>0</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
+      </c>
+      <c r="F222">
+        <v>0</v>
+      </c>
+      <c r="G222">
+        <v>0</v>
+      </c>
+      <c r="H222">
+        <v>0</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>36</v>
+      </c>
+      <c r="B223" t="s">
+        <v>11</v>
+      </c>
+      <c r="C223" t="s">
+        <v>24</v>
+      </c>
+      <c r="D223">
+        <v>115</v>
+      </c>
+      <c r="E223">
+        <v>507439</v>
+      </c>
+      <c r="F223">
+        <v>549</v>
+      </c>
+      <c r="G223">
+        <v>76832</v>
+      </c>
+      <c r="H223">
+        <v>83</v>
+      </c>
+      <c r="I223">
+        <v>584271</v>
+      </c>
+      <c r="J223">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>36</v>
+      </c>
+      <c r="B224" t="s">
+        <v>11</v>
+      </c>
+      <c r="C224" t="s">
+        <v>25</v>
+      </c>
+      <c r="D224">
+        <v>127</v>
+      </c>
+      <c r="E224">
+        <v>502486</v>
+      </c>
+      <c r="F224">
+        <v>543</v>
+      </c>
+      <c r="G224">
+        <v>66324</v>
+      </c>
+      <c r="H224">
+        <v>72</v>
+      </c>
+      <c r="I224">
+        <v>568810</v>
+      </c>
+      <c r="J224">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>36</v>
+      </c>
+      <c r="B225" t="s">
+        <v>11</v>
+      </c>
+      <c r="C225" t="s">
+        <v>26</v>
+      </c>
+      <c r="D225">
+        <v>0</v>
+      </c>
+      <c r="E225">
+        <v>0</v>
+      </c>
+      <c r="F225">
+        <v>0</v>
+      </c>
+      <c r="G225">
+        <v>0</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>36</v>
+      </c>
+      <c r="B226" t="s">
+        <v>27</v>
+      </c>
+      <c r="C226" t="s">
+        <v>28</v>
+      </c>
+      <c r="D226" s="1">
+        <v>15444</v>
+      </c>
+      <c r="E226">
+        <v>150755</v>
+      </c>
+      <c r="F226">
+        <v>40745</v>
+      </c>
+      <c r="G226">
+        <v>0</v>
+      </c>
+      <c r="H226">
+        <v>0</v>
+      </c>
+      <c r="I226">
+        <v>150755</v>
+      </c>
+      <c r="J226">
+        <v>40745</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>36</v>
+      </c>
+      <c r="B227" t="s">
+        <v>29</v>
+      </c>
+      <c r="C227" t="s">
+        <v>30</v>
+      </c>
+      <c r="D227" s="1">
+        <v>12251</v>
+      </c>
+      <c r="E227">
+        <v>42861</v>
+      </c>
+      <c r="F227">
+        <v>42861</v>
+      </c>
+      <c r="G227">
+        <v>0</v>
+      </c>
+      <c r="H227">
+        <v>0</v>
+      </c>
+      <c r="I227">
+        <v>42861</v>
+      </c>
+      <c r="J227">
+        <v>42861</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>36</v>
+      </c>
+      <c r="B228" t="s">
+        <v>27</v>
+      </c>
+      <c r="C228" t="s">
+        <v>31</v>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228">
+        <v>0</v>
+      </c>
+      <c r="F228">
+        <v>0</v>
+      </c>
+      <c r="G228">
+        <v>0</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>36</v>
+      </c>
+      <c r="B229" t="s">
+        <v>27</v>
+      </c>
+      <c r="C229" t="s">
+        <v>32</v>
+      </c>
+      <c r="D229">
+        <v>508</v>
+      </c>
+      <c r="E229">
+        <v>4948</v>
+      </c>
+      <c r="F229">
+        <v>1337</v>
+      </c>
+      <c r="G229">
+        <v>788</v>
+      </c>
+      <c r="H229">
+        <v>213</v>
+      </c>
+      <c r="I229">
+        <v>5736</v>
+      </c>
+      <c r="J229">
+        <v>1550</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>